--- a/tools/importer/reports/import-insurance-landing.report.xlsx
+++ b/tools/importer/reports/import-insurance-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>insurance-landing</t>
   </si>
   <si>
-    <t>2026-05-27T11:32:35.901Z</t>
+    <t>2026-05-28T11:18:18.555Z</t>
   </si>
   <si>
     <t>Car Insurance - Get a Free Auto Insurance Quote – Nationwide</t>
@@ -70,7 +70,7 @@
     <t>personal/insurance/claims</t>
   </si>
   <si>
-    <t>2026-05-27T11:46:24.424Z</t>
+    <t>2026-05-28T10:58:49.562Z</t>
   </si>
   <si>
     <t>File a Personal Insurance Claim Online - Nationwide</t>
@@ -88,7 +88,7 @@
     <t>personal/insurance/flood</t>
   </si>
   <si>
-    <t>2026-05-27T11:35:19.723Z</t>
+    <t>2026-05-28T11:05:50.471Z</t>
   </si>
   <si>
     <t>Flood Insurance Coverage from Nationwide</t>
@@ -106,7 +106,7 @@
     <t>personal/insurance/golf-cart</t>
   </si>
   <si>
-    <t>2026-05-27T11:38:10.438Z</t>
+    <t>2026-05-28T11:08:28.544Z</t>
   </si>
   <si>
     <t>Golf Cart Insurance – Nationwide</t>
@@ -124,7 +124,7 @@
     <t>personal/insurance/homeowners</t>
   </si>
   <si>
-    <t>2026-05-27T11:31:37.129Z</t>
+    <t>2026-05-28T10:57:56.797Z</t>
   </si>
   <si>
     <t>Homeowners Insurance Quotes - Nationwide</t>
@@ -142,7 +142,7 @@
     <t>personal/insurance/identity-theft</t>
   </si>
   <si>
-    <t>2026-05-27T11:34:24.790Z</t>
+    <t>2026-05-28T11:04:56.726Z</t>
   </si>
   <si>
     <t>Identity Theft Insurance – Nationwide</t>
@@ -160,7 +160,7 @@
     <t>personal/insurance/life</t>
   </si>
   <si>
-    <t>2026-05-27T11:28:04.674Z</t>
+    <t>2026-05-28T10:54:24.903Z</t>
   </si>
   <si>
     <t>Life Insurance – Get an Affordable Quote – Nationwide</t>
@@ -178,7 +178,7 @@
     <t>personal/insurance/member-resources</t>
   </si>
   <si>
-    <t>2026-05-27T11:37:17.386Z</t>
+    <t>2026-05-28T11:07:35.367Z</t>
   </si>
   <si>
     <t>Member Resource Guide to Services &amp; Benefits – Nationwide</t>
@@ -196,7 +196,7 @@
     <t>personal/insurance/motorcycle</t>
   </si>
   <si>
-    <t>2026-05-27T11:29:51.758Z</t>
+    <t>2026-05-28T10:56:10.612Z</t>
   </si>
   <si>
     <t>Motorcycle Insurance Quotes from Nationwide</t>
@@ -211,7 +211,7 @@
     <t>personal/insurance/pet</t>
   </si>
   <si>
-    <t>2026-05-27T11:39:56.726Z</t>
+    <t>2026-05-28T11:10:15.434Z</t>
   </si>
   <si>
     <t>Pet Health Insurance – Nationwide</t>
@@ -229,7 +229,7 @@
     <t>personal/insurance/policy-reviews</t>
   </si>
   <si>
-    <t>2026-05-27T11:39:04.180Z</t>
+    <t>2026-05-28T11:09:20.991Z</t>
   </si>
   <si>
     <t>Annual Policy Review – Nationwide</t>
@@ -244,7 +244,7 @@
     <t>personal/insurance/renters</t>
   </si>
   <si>
-    <t>2026-05-27T11:28:57.741Z</t>
+    <t>2026-05-28T10:55:18.635Z</t>
   </si>
   <si>
     <t>Renters Insurance Quotes - Nationwide</t>
@@ -262,7 +262,7 @@
     <t>personal/insurance/rv</t>
   </si>
   <si>
-    <t>2026-05-27T11:36:13.020Z</t>
+    <t>2026-05-28T11:06:43.353Z</t>
   </si>
   <si>
     <t>RV Insurance Quotes – Nationwide</t>
@@ -280,7 +280,7 @@
     <t>personal/insurance/snowmobile</t>
   </si>
   <si>
-    <t>2026-05-27T11:30:44.238Z</t>
+    <t>2026-05-28T10:57:03.645Z</t>
   </si>
   <si>
     <t>Snowmobile Insurance and Quotes – Nationwide</t>
@@ -298,7 +298,7 @@
     <t>personal/insurance/vehicle</t>
   </si>
   <si>
-    <t>2026-05-27T11:40:48.725Z</t>
+    <t>2026-05-28T11:11:08.930Z</t>
   </si>
   <si>
     <t>Vehicle Insurance Products – Nationwide</t>

--- a/tools/importer/reports/import-insurance-landing.report.xlsx
+++ b/tools/importer/reports/import-insurance-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>insurance-landing</t>
   </si>
   <si>
-    <t>2026-05-28T11:18:18.555Z</t>
+    <t>2026-05-29T11:59:37.280Z</t>
   </si>
   <si>
     <t>Car Insurance - Get a Free Auto Insurance Quote – Nationwide</t>
@@ -70,7 +70,7 @@
     <t>personal/insurance/claims</t>
   </si>
   <si>
-    <t>2026-05-28T10:58:49.562Z</t>
+    <t>2026-05-29T12:04:58.724Z</t>
   </si>
   <si>
     <t>File a Personal Insurance Claim Online - Nationwide</t>
@@ -88,7 +88,7 @@
     <t>personal/insurance/flood</t>
   </si>
   <si>
-    <t>2026-05-28T11:05:50.471Z</t>
+    <t>2026-05-29T12:06:47.446Z</t>
   </si>
   <si>
     <t>Flood Insurance Coverage from Nationwide</t>
@@ -106,7 +106,7 @@
     <t>personal/insurance/golf-cart</t>
   </si>
   <si>
-    <t>2026-05-28T11:08:28.544Z</t>
+    <t>2026-05-29T12:09:28.576Z</t>
   </si>
   <si>
     <t>Golf Cart Insurance – Nationwide</t>
@@ -124,7 +124,7 @@
     <t>personal/insurance/homeowners</t>
   </si>
   <si>
-    <t>2026-05-28T10:57:56.797Z</t>
+    <t>2026-05-29T12:04:05.833Z</t>
   </si>
   <si>
     <t>Homeowners Insurance Quotes - Nationwide</t>
@@ -142,7 +142,7 @@
     <t>personal/insurance/identity-theft</t>
   </si>
   <si>
-    <t>2026-05-28T11:04:56.726Z</t>
+    <t>2026-05-29T12:05:53.063Z</t>
   </si>
   <si>
     <t>Identity Theft Insurance – Nationwide</t>
@@ -160,7 +160,7 @@
     <t>personal/insurance/life</t>
   </si>
   <si>
-    <t>2026-05-28T10:54:24.903Z</t>
+    <t>2026-05-29T12:00:32.249Z</t>
   </si>
   <si>
     <t>Life Insurance – Get an Affordable Quote – Nationwide</t>
@@ -178,7 +178,7 @@
     <t>personal/insurance/member-resources</t>
   </si>
   <si>
-    <t>2026-05-28T11:07:35.367Z</t>
+    <t>2026-05-29T12:08:35.590Z</t>
   </si>
   <si>
     <t>Member Resource Guide to Services &amp; Benefits – Nationwide</t>
@@ -196,7 +196,7 @@
     <t>personal/insurance/motorcycle</t>
   </si>
   <si>
-    <t>2026-05-28T10:56:10.612Z</t>
+    <t>2026-05-29T12:02:19.242Z</t>
   </si>
   <si>
     <t>Motorcycle Insurance Quotes from Nationwide</t>
@@ -211,7 +211,7 @@
     <t>personal/insurance/pet</t>
   </si>
   <si>
-    <t>2026-05-28T11:10:15.434Z</t>
+    <t>2026-05-29T12:11:13.149Z</t>
   </si>
   <si>
     <t>Pet Health Insurance – Nationwide</t>
@@ -229,7 +229,7 @@
     <t>personal/insurance/policy-reviews</t>
   </si>
   <si>
-    <t>2026-05-28T11:09:20.991Z</t>
+    <t>2026-05-29T12:10:21.542Z</t>
   </si>
   <si>
     <t>Annual Policy Review – Nationwide</t>
@@ -244,7 +244,7 @@
     <t>personal/insurance/renters</t>
   </si>
   <si>
-    <t>2026-05-28T10:55:18.635Z</t>
+    <t>2026-05-29T12:01:24.729Z</t>
   </si>
   <si>
     <t>Renters Insurance Quotes - Nationwide</t>
@@ -262,7 +262,7 @@
     <t>personal/insurance/rv</t>
   </si>
   <si>
-    <t>2026-05-28T11:06:43.353Z</t>
+    <t>2026-05-29T12:07:42.304Z</t>
   </si>
   <si>
     <t>RV Insurance Quotes – Nationwide</t>
@@ -280,7 +280,7 @@
     <t>personal/insurance/snowmobile</t>
   </si>
   <si>
-    <t>2026-05-28T10:57:03.645Z</t>
+    <t>2026-05-29T12:03:13.944Z</t>
   </si>
   <si>
     <t>Snowmobile Insurance and Quotes – Nationwide</t>
@@ -298,7 +298,7 @@
     <t>personal/insurance/vehicle</t>
   </si>
   <si>
-    <t>2026-05-28T11:11:08.930Z</t>
+    <t>2026-05-29T12:12:05.925Z</t>
   </si>
   <si>
     <t>Vehicle Insurance Products – Nationwide</t>
